--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Baburaja Maharjan</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841479122</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841479122</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1115,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.65564</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.65564</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1168,25 +1164,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.3402</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.3402</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1287,10 +1279,8 @@
           <t>Dinesh Agrawal</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9801172900</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9801172900</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1376,10 +1366,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1390,7 +1378,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -80,19 +77,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -112,23 +103,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -504,60 +486,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Employee Name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -583,50 +583,50 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task / Issue Type</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total_Tickets</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Solved_Count</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>% Share of Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -643,55 +643,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>2</v>
+      <c r="D2" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>2</v>
+      <c r="D3" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -739,10 +751,10 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -751,7 +763,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -761,652 +773,880 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Target Employee</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Grid Date</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Grid User Name</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Grid Employee Name</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Grid Module</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Grid Operation</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Grid IP Address</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Grid Remark</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Case Origin</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Mobile No</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Sub Sub Category</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Estimated closed time based on SLA</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Estimated closed time based on TAT</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>User Id</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Associated Location Status</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Case Reason</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Assign Team</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Assign User</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Customer Address</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="AH1" s="2" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Escalated Layer</t>
         </is>
       </c>
-      <c r="AI1" s="2" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="AJ1" s="2" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>SLA Left/Total</t>
         </is>
       </c>
-      <c r="AK1" s="2" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>TAT Left/Total</t>
         </is>
       </c>
-      <c r="AL1" s="2" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="AM1" s="2" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Last Modified By</t>
         </is>
       </c>
-      <c r="AN1" s="2" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Associated Location Level</t>
         </is>
       </c>
-      <c r="AO1" s="2" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Associated Location Name</t>
         </is>
       </c>
-      <c r="AP1" s="2" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="AQ1" s="2" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Solution Given</t>
         </is>
       </c>
-      <c r="AR1" s="2" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="AS1" s="2" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="AT1" s="2" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
-      <c r="AU1" s="2" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="AV1" s="2" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="AW1" s="2" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Task / Issue Type</t>
         </is>
       </c>
-      <c r="AX1" s="2" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Employee Name</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 9:14 AM</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 9:55 AM</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>wifi6</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>TKT1358080</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Baburaja Maharjan</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>On Hold</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>TKT1356816</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Bishal Regmi</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>Baburaja Maharjan</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>9841479122</v>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Bishal Regmi</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>9841932852</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 09:14:22 AM</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9841479122</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 09:14:22 AM</t>
-        </is>
-      </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:55:01 AM</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>9841932852</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 04:39:49 PM</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:55:01 AM</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="n">
-        <v>27.65564</v>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>27.75124</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC2" s="3" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD2" s="3" t="inlineStr"/>
-      <c r="AE2" s="3" t="inlineStr">
-        <is>
-          <t>27.65564, 85.3402, New Ganesh Temple Naya Basti, M84Q+9V5, Mahalaxmi 44700, Bagmati, Central, Nepal</t>
-        </is>
-      </c>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>Near Grande Villa,Tokha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>rgmibishal55@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr">
-        <is>
-          <t>Sunita Yonjan</t>
-        </is>
-      </c>
-      <c r="AM2" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AN2" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO2" s="3" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="n">
-        <v>85.3402</v>
-      </c>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>03:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AK2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>L3-1</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>85.32164</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>18h 44m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>1d 17h 15m</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX2" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 9:14 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>TKT1358080</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>9841479122</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:14:22 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>9841479122</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:29:39 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:14:22 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>27.65564</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>27.65564, 85.3402, New Ganesh Temple Naya Basti, M84Q+9V5, Mahalaxmi 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP3" s="2" t="inlineStr">
+        <is>
+          <t>85.3402</t>
+        </is>
+      </c>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="2" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="2" t="inlineStr">
+        <is>
+          <t>18h 44m</t>
+        </is>
+      </c>
+      <c r="AU3" s="2" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="2" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="2" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>05 Oct 2026 9:09 AM</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Wifi 6</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>TKT1357958</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Dinesh Agrawal</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Dinesh Agrawal</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n">
-        <v>9801172900</v>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>9801172900</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>04 Oct 2026 01:33:21 PM</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>LTP9705346755</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>04 Oct 2026 01:33:21 PM</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>05 Oct 2026 09:09:33 AM</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr"/>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>Laxman Koirala</t>
         </is>
       </c>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr"/>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>Imadol Imadol, Kathmandu, Nepal, Nepal</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AF4" s="2" t="inlineStr">
         <is>
           <t>kclalita910@gmail.com</t>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AG4" s="2" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr">
         <is>
           <t>Sandesh Ghale</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AM4" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AN4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="2" t="inlineStr">
         <is>
           <t>L43-6</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="2" t="inlineStr">
         <is>
           <t>19h 36m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
+      <c r="AT4" s="2" t="inlineStr">
         <is>
           <t>19h 36m</t>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AU4" s="2" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
+      <c r="AV4" s="2" t="inlineStr">
         <is>
           <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AW4" s="2" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AX4" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -77,13 +80,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -103,14 +112,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,78 +504,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Employee Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -572,10 +590,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -583,52 +601,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Task / Issue Type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Total_Tickets</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Solved_Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>% Share of Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -653,57 +694,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>3</v>
+      <c r="C2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>3</v>
+      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -717,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -728,7 +769,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -751,7 +792,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -768,887 +809,1071 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Target Employee</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Grid Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Grid User Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grid Employee Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grid Module</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grid Operation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grid IP Address</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grid Remark</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Case Origin</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Mobile No</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sub Sub Category</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Estimated closed time based on SLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Estimated closed time based on TAT</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>User Id</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Status</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Case Reason</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>Assign Team</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Assign User</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>Customer Address</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>Escalated Layer</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" s="2" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" s="2" t="inlineStr">
         <is>
           <t>SLA Left/Total</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" s="2" t="inlineStr">
         <is>
           <t>TAT Left/Total</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" s="2" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" s="2" t="inlineStr">
         <is>
           <t>Last Modified By</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Level</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Name</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" s="2" t="inlineStr">
         <is>
           <t>Solution Given</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" s="2" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" s="2" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" s="2" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" s="2" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" s="2" t="inlineStr">
         <is>
           <t>Task / Issue Type</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" s="2" t="inlineStr">
         <is>
           <t>Employee Name</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 9:55 AM</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>wifi6</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>TKT1356816</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Bishal Regmi</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Bishal Regmi</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="n">
+        <v>9841932852</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:55:01 AM</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>9841932852</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 04:39:49 PM</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:55:01 AM</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>27.75124</v>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 09:55:01 AM</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>9841932852</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 04:39:49 PM</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 09:55:01 AM</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>27.75124</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr"/>
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>Near Grande Villa,Tokha, Bagmati, Central, Nepal</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <t>rgmibishal55@gmail.com</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <t>03:21 hour</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <t>Ishlok Shahi</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L3-1</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>85.32164</t>
-        </is>
-      </c>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="n">
+        <v>85.32164</v>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 15m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT2" s="2" t="inlineStr">
-        <is>
-          <t>1d 17h 15m</t>
-        </is>
-      </c>
-      <c r="AU2" s="2" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV2" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX2" s="2" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 9:14 AM</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>wifi6</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>TKT1358080</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Baburaja Maharjan</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Baburaja Maharjan</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="3" t="n">
+        <v>9841479122</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:14:22 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>9841479122</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:29:39 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:14:22 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>27.65564</v>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 09:14:22 AM</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>9841479122</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>05 Oct 2026 09:14:22 AM</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>27.65564</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>27.65564, 85.3402, New Ganesh Temple Naya Basti, M84Q+9V5, Mahalaxmi 44700, Bagmati, Central, Nepal</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>Sunita Yonjan</t>
         </is>
       </c>
-      <c r="AM3" s="2" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AO3" s="2" t="inlineStr">
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP3" s="2" t="inlineStr">
-        <is>
-          <t>85.3402</t>
-        </is>
-      </c>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr">
+      <c r="AP3" s="3" t="n">
+        <v>85.3402</v>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>18h 44m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS3" s="2" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT3" s="2" t="inlineStr">
-        <is>
-          <t>18h 44m</t>
-        </is>
-      </c>
-      <c r="AU3" s="2" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV3" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW3" s="2" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX3" s="2" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 9:09 AM</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Wifi 6</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>TKT1357958</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Dinesh Agrawal</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Dinesh Agrawal</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>9801172900</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="3" t="n">
+        <v>9801172900</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 01:33:21 PM</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>LTP9705346755</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 01:33:21 PM</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 09:09:33 AM</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Laxman Koirala</t>
         </is>
       </c>
-      <c r="AC4" s="2" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>Imadol Imadol, Kathmandu, Nepal, Nepal</t>
         </is>
       </c>
-      <c r="AF4" s="2" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>kclalita910@gmail.com</t>
         </is>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>Sandesh Ghale</t>
         </is>
       </c>
-      <c r="AM4" s="2" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="2" t="inlineStr">
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L43-6</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>19h 36m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>19h 36m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 9:59 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358398</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Prabodh Thapa</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Prabodh Thapa</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9844041672</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:19:44 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>KLK9844041672</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:19:44 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:59:08 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Danphe Colony - Housing development Q82M+R2J Danphe Colony Road Kathmandu 44600, Kathmandu, Nepal, N</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>thapaprabodh7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>L43-6</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AS4" s="2" t="inlineStr">
-        <is>
-          <t>19h 36m</t>
-        </is>
-      </c>
-      <c r="AT4" s="2" t="inlineStr">
-        <is>
-          <t>19h 36m</t>
-        </is>
-      </c>
-      <c r="AU4" s="2" t="inlineStr">
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L12-3</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>16h 39m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>16h 39m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV4" s="2" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW4" s="2" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX4" s="2" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,54 +528,90 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -634,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -657,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -684,13 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +739,25 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -722,29 +770,63 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>4</v>
+      <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="D4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>4</v>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -758,18 +840,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -798,7 +880,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1740,10 +1822,8 @@
           <t>Prabodh Thapa</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9844041672</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9844041672</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1829,10 +1909,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1843,29 +1921,29 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>16h 39m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>16h 39m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>16h 39m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>16h 39m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1874,6 +1952,646 @@
       <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:09 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358296</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Sita Rai</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Sita Rai</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9860777544</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:09:33 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>CHB9860777544</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:25:36 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:09:33 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Aarubari Chowk Bus Stop - Bus stop Gokarneshwor 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>00:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>17h 43m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:07 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>5g not connecting</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354775</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Sohil Manandhar</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Sohil Manandhar</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9843670380</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:00:34 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9843670380</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:50:55 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:07:21 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.68931</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Thankot,NCC Bank, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>sohil.mndhr53@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>20:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB121</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.22653</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 6m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:06 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>5g not connecting</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354775</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sohil Manandhar</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Sohil Manandhar</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9843670380</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:00:34 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9843670380</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:50:55 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:07:21 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.68931</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Thankot,NCC Bank, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>sohil.mndhr53@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>20:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB121</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.22653</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 6m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
@@ -808,25 +808,69 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>6</v>
+      <c r="F6" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -840,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -851,14 +895,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -868,14 +912,14 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -2022,10 +2066,8 @@
           <t>Sita Rai</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9860777544</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9860777544</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2115,10 +2157,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2129,7 +2169,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2230,10 +2270,8 @@
           <t>Sohil Manandhar</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9843670380</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9843670380</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2268,10 +2306,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.68931</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.68931</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2327,25 +2363,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>CDB121</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.22653</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.22653</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2446,10 +2478,8 @@
           <t>Sohil Manandhar</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9843670380</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9843670380</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2484,10 +2514,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.68931</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.68931</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2543,47 +2571,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>CDB121</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.22653</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.22653</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 6m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 6m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>3d 1h 16m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : 5g not connecting   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -2592,6 +2616,318 @@
       <c r="AX8" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:22 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr"/>
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr"/>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:27 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>router adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358328</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Anish bhujel</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Anish bhujel</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9818757588</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:27:46 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9822072768</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:44:07 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:27:46 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>27.723089, 85.351429 - Kathmandu Metropolitan, Kathmandu, Bagmati, Central, Nepal27.723089, 85.35142</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>00:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L63-7</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>17h 43m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -546,72 +546,90 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>55.6%</t>
+      <c r="B7" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -693,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -720,15 +738,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -739,25 +758,30 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -779,10 +803,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>5</v>
+      <c r="G2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -801,9 +828,12 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -817,15 +847,18 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -836,10 +869,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -847,7 +880,10 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -858,19 +894,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>8</v>
+      <c r="G6" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -884,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -897,10 +936,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="39" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -918,13 +957,13 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -2794,10 +2833,8 @@
           <t>Anish bhujel</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9818757588</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9818757588</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2883,10 +2920,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2897,37 +2932,673 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>17h 43m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : router adapter damage issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:42 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358995</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Denish shrestha</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Denish shrestha</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841767564</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:42:08 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841767564</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:00:19 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:42:08 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Okhaldhunga chowk Pepsi ko depo, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>00:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L12-3</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>17h 43m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>41m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : router adapter damage issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:46 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357042</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Sirjanshil Publication pvt ltd</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Sirjanshil Publication pvt ltd</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9867815013</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX10" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:46:45 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9867815013</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 07:29:57 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:46:45 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.68435</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Kalikamarga, Opposite to Beautiful Coffee Nepal, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>bibeksirjanshil@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>01:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.30643</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 16m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357042</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Sirjanshil Publication pvt ltd</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Sirjanshil Publication pvt ltd</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9867815013</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:46:45 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9867815013</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 07:29:57 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:46:45 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.68435</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Kalikamarga, Opposite to Beautiful Coffee Nepal, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>bibeksirjanshil@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>01:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.30643</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 16m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -969,7 +969,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3033,10 +3033,8 @@
           <t>Denish shrestha</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841767564</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841767564</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3122,10 +3120,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -3136,7 +3132,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3227,20 +3223,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Bibek Sirjanshil Publication pvt ltd</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9867815013</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9867815013</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3275,10 +3265,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.68435</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.68435</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3334,25 +3322,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.30643</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.30643000000001</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3443,20 +3427,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Bibek Sirjanshil Publication pvt ltd</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9867815013</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9867815013</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3491,10 +3469,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.68435</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.68435</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3550,47 +3526,43 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.30643</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.30643000000001</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 16m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>1d 15h 16m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -3599,6 +3571,222 @@
       <c r="AX13" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:53 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:59 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -800,16 +800,16 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -900,16 +900,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -952,7 +952,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -969,7 +969,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3790,6 +3790,646 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:16 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358932</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Hera Kumari Tamang Lama</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Hera Kumari Tamang Lama</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9861917065</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:16:36 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9861917065</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:02:42 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:16:36 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.721976</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Lazimpat Rd, Kathmandu 44616, near by Big Mart, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>tamangsudip554@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>01:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.310055</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2h 13m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:05 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357530</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Koswar</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Koswar</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9851075466</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:15:10 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851075466</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:15:10 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:05:31 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Bauthali Chowk Bus Stop - Bus stop Chandragiri 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>01:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB321</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>1d 50m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 50m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357530</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Koswar</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Koswar</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9851075466</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:15:10 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851075466</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:15:10 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:05:31 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Bauthali Chowk Bus Stop - Bus stop Chandragiri 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>01:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB321</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>1d 50m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 50m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -969,7 +969,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3857,10 +3857,8 @@
           <t>Hera Kumari Tamang Lama</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9861917065</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9861917065</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3895,10 +3893,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.721976</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.721976</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3954,25 +3950,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>1,6</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.310055</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.31005500000001</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4073,10 +4065,8 @@
           <t>Saurav Koswar</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9851075466</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9851075466</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4148,10 +4138,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH17" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH17" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
@@ -4170,10 +4158,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4184,7 +4170,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4285,10 +4271,8 @@
           <t>Saurav Koswar</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9851075466</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9851075466</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4360,10 +4344,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH18" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
@@ -4382,10 +4364,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4396,7 +4376,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -700,30 +700,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>80.0%</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>58.8%</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -738,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -840,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -850,13 +873,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
@@ -865,17 +888,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -888,28 +911,53 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>12</v>
+      <c r="F7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -969,7 +1017,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4410,6 +4458,550 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:33 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:36 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv  setbox issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr"/>
+      <c r="V21" s="3" t="inlineStr"/>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr"/>
+      <c r="AA21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AC21" s="3" t="inlineStr"/>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv  setbox issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv remote issue    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>iptv remote issue</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355951</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Santa Maya Nagarkoti</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Santa Maya Nagarkoti</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9808133564</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:34:51 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9808133564</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:33:24 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:43:45 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.67897</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Our Mart, Kanchan Basti, Matatirtha,Kanchan Basti, Satungal-Matatirtha Road, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>rameshcaagiri@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>11:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB247</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.24285</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv remote issue    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 8m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2d 15h 10m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv remote issue    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -761,10 +761,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -826,13 +826,13 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -913,14 +913,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -936,28 +936,53 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>13</v>
+      <c r="F8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX22"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1006,7 +1031,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -4849,10 +4874,8 @@
           <t>Santa Maya Nagarkoti</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9808133564</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9808133564</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4887,10 +4910,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.67897</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.67897</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4928,10 +4949,8 @@
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="AH22" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH22" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
@@ -4950,47 +4969,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>CDB247</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.24285</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.24285</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 8m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2d 15h 10m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv remote issue    has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 8m</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>2d 15h 10m</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv remote issue    has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -4999,6 +5014,438 @@
       <c r="AX22" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:52 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Secondary router   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Secondary router</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357540</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Rat bahadur shrestha</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Rat bahadur shrestha</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9851362036</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:52:55 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851362036</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:17:19 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:52:55 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.685044</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Buddhanagar, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>01:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB018</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.328915</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Secondary router   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 35m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Secondary router   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:52 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357939</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Joshi</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Joshi</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9841430889</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:52:25 AM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9841430889</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:27:37 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:52:25 AM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.662359</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Pandubazar Height, Katunje-8, near Royal Dynasty Village Resort, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>rajanjoshi14@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>01:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L30-5</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.4179</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>22h 24m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -838,7 +838,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -863,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -913,17 +913,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -938,14 +938,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -961,28 +961,53 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="D9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>15</v>
+      <c r="G9" s="4" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5084,10 +5109,8 @@
           <t>Rat bahadur shrestha</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9851362036</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9851362036</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5122,10 +5145,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.685044</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.685044</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5181,25 +5202,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>CDB018</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.328915</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.32891499999999</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : Secondary router   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5290,20 +5307,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M24" s="3" t="inlineStr"/>
       <c r="N24" s="3" t="inlineStr">
         <is>
           <t>Rajan Joshi</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9841430889</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9841430889</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5338,10 +5349,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.662359</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.662359</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5397,55 +5406,263 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>L30-5</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.4179</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.4179</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>22h 24m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:11 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>No light in stb</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358403</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9851045120</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:11:54 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851045120</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:24:33 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:11:54 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Sunflower Academy (English Medium SS) - Educational institution Q822+54F way Tarakeshwar 44600, Bagm</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>9851045120@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>02:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>22h 24m</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>18h 47m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW24" s="3" t="inlineStr">
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX24" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3</v>
@@ -832,13 +832,13 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -863,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -873,13 +873,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -898,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
@@ -986,28 +986,53 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>16</v>
+      <c r="G10" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX25"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5511,20 +5536,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Dinesh Shrestha</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9851045120</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9851045120</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5596,10 +5615,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
@@ -5618,10 +5635,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5632,37 +5647,573 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>18h 47m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : No light in stb  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:31 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : kam nai nalagne net  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>kam nai nalagne net</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357131</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>BHISAN RAI</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>BHISAN RAI</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9861304002</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:31:07 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851156468</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:57:48 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:31:07 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.678557</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Kamerotar Land Polling Project Bappa, M9FR+Q53, ??????? ????, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>rbsn.architects@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>02:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L53-3</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.391609</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : kam nai nalagne net  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>18h 47m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 33m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : No light in stb  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW25" s="3" t="inlineStr">
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : kam nai nalagne net  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX25" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359158</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Ashim Shrestha</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Ashim Shrestha</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9761878351</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:18:48 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>CHB9761878351</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:22:09 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:18:48 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>27.74451,85.33298, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>9761878351@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>00:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L12-1</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>56m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:27 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -829,10 +829,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1029,10 +1029,10 @@
         <v>4</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5748,10 +5748,8 @@
           <t>BHISAN RAI</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9861304002</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9861304002</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5786,10 +5784,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.678557</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.678557</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5845,25 +5841,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L53-3</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.391609</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.391609</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : kam nai nalagne net  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5964,10 +5956,8 @@
           <t>Ashim Shrestha</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9761878351</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9761878351</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6039,10 +6029,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH27" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH27" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
@@ -6061,10 +6049,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -6075,7 +6061,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6217,6 +6203,214 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:40 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356209</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Arjun Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Arjun Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9709913337</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:28:03 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>KLK9709913337</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:28:03 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:40:54 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Academy - Middle school P75G+2M3 Nagarjun 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>9709913337@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>12:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 12m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 12m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.7%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>4</v>
@@ -1032,7 +1032,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX29"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1080,7 +1080,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -6270,10 +6270,8 @@
           <t>Arjun Bahadur Singh</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9709913337</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9709913337</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6363,10 +6361,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6377,29 +6373,29 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 12m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 12m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>2d 3h 12m</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>2d 3h 12m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -6408,6 +6404,650 @@
       <c r="AX29" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:54 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359225</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Maharjan</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Maharjan</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9840235129</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:54:33 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9840235129</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:51:55 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:54:33 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Near Napi Karyalaya Manamaiju, Unnamed Road, Kathmandu 44600, P8W7+49M, Kathmandu 44600, Bagmati, Ce</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>rabinmaharjan916@gamil.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>01:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L46-5</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1h 2m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:58 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357946</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Merina Shrestha</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Merina Shrestha</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9823865787</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9823865787</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:29:55 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.68341</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Tinkune, Kathmandu-32, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>sth.meri@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>02:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>CDB188</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.34399</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>23h 28m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359190</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9803803944</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:47:46 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9803803944</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:39:17 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:47:46 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.733464</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Helambu Driving School - Drivers license training school P9M6+9FH, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>01:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.361761</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>1h 8m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -829,10 +829,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1029,10 +1029,10 @@
         <v>4</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6474,10 +6474,8 @@
           <t>Rabi Maharjan</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9840235129</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9840235129</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6549,10 +6547,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH30" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH30" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
@@ -6571,10 +6567,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6585,7 +6579,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6686,10 +6680,8 @@
           <t>Merina Shrestha</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9823865787</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9823865787</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6724,10 +6716,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.68341</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.68341</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6783,25 +6773,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>CDB188</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.34399</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.34399000000001</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6902,10 +6888,8 @@
           <t>Chandra Bahadur Thapa</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9803803944</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9803803944</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6940,10 +6924,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.733464</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.733464</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6977,10 +6959,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH32" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH32" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
@@ -6999,47 +6979,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.361761</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.361761</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>1h 8m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>1h 8m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7048,6 +7024,222 @@
       <c r="AX32" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 1:13 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358103</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Lalit Kumar Sunuwar</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Lalit Kumar Sunuwar</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9860553444</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:43:16 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9860553444</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:43:16 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:13:37 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.70776</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu, Nagarjun, Sitapaila, near at Jyoti Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>lalitfloyd@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>03:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.27537</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>22h 30m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>22h 30m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
@@ -832,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>6</v>
@@ -1032,7 +1032,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7094,10 +7094,8 @@
           <t>Lalit Kumar Sunuwar</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9860553444</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9860553444</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7132,10 +7130,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.70776</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.70776</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -7191,47 +7187,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>2,3</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.27537</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.27537</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>22h 30m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>22h 30m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>22h 30m</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>22h 30m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7240,6 +7232,426 @@
       <c r="AX33" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 1:23 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358388</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Gautam Banerjee</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Gautam Banerjee</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9851014012</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:23:05 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9851014012</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:14:10 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:23:05 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.71452</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Backside of Sirjana Secondary School,Jorpati,kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>banerjeefalgun@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>03:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>L59-6</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.36912</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>20h 8m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 1:28 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358206</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Sudin shrestha</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Sudin shrestha</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9851086393</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:28:58 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9851086393</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:37:41 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:28:58 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>New baneshwor Near RBB Bank	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>03:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L41-1</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>21h 51m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1026,13 +1026,13 @@
         <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX35"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7302,10 +7302,8 @@
           <t>Gautam Banerjee</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9851014012</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9851014012</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7340,10 +7338,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.71452</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.71452</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -7399,25 +7395,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>L59-6</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.36912</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.36912</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7518,10 +7510,8 @@
           <t>Sudin shrestha</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9851086393</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9851086393</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7607,10 +7597,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7621,37 +7609,249 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>21h 51m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 1:39 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358564</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>ranju paudel</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>ranju paudel</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9849512384</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:39:07 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9849512384</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 07:16:30 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:39:07 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.660731</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>27.660332, 85.364638, Near by Mahalaxmi Municipality Ward No. 07, Office, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>03:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>L27-8</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.364919</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>21h 51m</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>18h 22m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW35" s="3" t="inlineStr">
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
@@ -832,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -863,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -898,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
@@ -913,7 +913,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -938,17 +938,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -963,14 +963,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -988,20 +988,20 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1011,28 +1011,53 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="4" t="n">
+      <c r="C11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>26</v>
+      <c r="G11" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1073,7 +1098,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -1090,7 +1115,7 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -7710,10 +7735,8 @@
           <t>ranju paudel</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9849512384</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9849512384</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7748,10 +7771,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.660731</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.660731</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7803,55 +7824,467 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>L27-8</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.364919</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.364919</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>18h 22m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>STB connection</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357113</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Thapa</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Thapa</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9767483764</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:57:51 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>KLK9767483764</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:30:41 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:57:51 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.701463887608504</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>ktm manamaijuengal hot school, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>thapa76@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr"/>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L31-5</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.3304672241211</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>18h 22m</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 27m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 1:54 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359134</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Ram shekhar das</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Ram shekhar das</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9869644288</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:54:38 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9869644288</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 11:11:26 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:54:38 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Jorpati	Jambu danda gate	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>02:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>L61-5A</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2h 43m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW36" s="3" t="inlineStr">
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX36" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
@@ -832,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1045,7 +1045,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>7</v>
@@ -1057,7 +1057,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1098,14 +1098,14 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -7939,10 +7939,8 @@
           <t>Preeti Thapa</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9767483764</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9767483764</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7977,10 +7975,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.701463887608504</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.7014638876085</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -8032,25 +8028,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>L31-5</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.3304672241211</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.33046722412109</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : STB connection  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -8151,10 +8143,8 @@
           <t>Ram shekhar das</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9869644288</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9869644288</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8240,10 +8230,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -8254,35 +8242,251 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2h 43m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 2:13 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359287</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Dhakal Bahadur Budathoki</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Dhakal Bahadur Budathoki</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9852840707</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:13:15 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9852840707</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:30:53 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:13:15 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.72203</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Boudha Rd, Gokarneshwor, Near Sindhupalchok Alon Bhojanalay, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>dhakalbudathoki99@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>01:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>L50-8</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.3737</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>2h 43m</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1h 42m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW38" s="3" t="inlineStr">
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX38" s="3" t="inlineStr">
+      <c r="AX39" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.5%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -829,10 +829,10 @@
         <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1054,10 +1054,10 @@
         <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX39"/>
+  <dimension ref="A1:AX41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8343,10 +8343,8 @@
           <t>Dhakal Bahadur Budathoki</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9852840707</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9852840707</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8381,10 +8379,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.72203</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.72203</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -8440,47 +8436,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>L50-8</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.3737</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.3737</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1h 42m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>1h 42m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -8489,6 +8481,330 @@
       <c r="AX39" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="AA40" s="3" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr"/>
+      <c r="AC40" s="3" t="inlineStr"/>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr"/>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr"/>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr"/>
+      <c r="AM40" s="3" t="inlineStr"/>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 2:31 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357615</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Shrestha</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Shrestha</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9860573734</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:49:39 AM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9860573734</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:49:39 AM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:31:35 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.70721</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Bafal, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>kamalshrestha1997@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>04:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB108</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.27434</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 41m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 41m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1042,22 +1042,22 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>8</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>7</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX41"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8659,10 +8659,8 @@
           <t>Kamal Shrestha</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9860573734</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9860573734</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8697,10 +8695,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.70721</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.70721</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8756,55 +8752,903 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB108</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.27434</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.27434</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 41m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 41m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 41m</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 41m</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 2:34 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router ko lagi   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router ko lagi</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359293</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Kapindra Giri</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Kapindra Giri</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9849931051</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:34:49 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9849931051</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 12:37:41 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:34:49 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.71942</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Jorpati-Sankhu Rd, Gokarneshwor, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>kapindra04@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>01:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr"/>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L12-6</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.38795</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router ko lagi   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1h 57m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router ko lagi   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 2:32 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Replacement   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357967</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Bhagat</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Bhagat</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9820991172</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:32:19 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>CHB9520991172</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:36:34 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:32:19 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Shanti nagar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>rb3121624@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>04:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr"/>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L4-7</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Replacement   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 55m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Replacement   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 2:33 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357595</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Mandala International School</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Mandala International School</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9705404836</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:40:27 AM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9851161445</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:40:27 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:33:27 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.6982</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>kathmandu bagmati nagaarjun municipality , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>bhattarai71@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>04:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.27581</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 53m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 53m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV41" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW41" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX41" s="3" t="inlineStr">
+      <c r="AX44" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 2:43 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359354</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Padam Roka</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Padam Roka</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9861027818</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:43:14 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9861027818</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:10:44 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:43:14 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.73035</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Venus college	Sangrila khadhya store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr"/>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>01:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.378552</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1h 32m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -8867,10 +8867,8 @@
           <t>Kapindra Giri</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9849931051</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9849931051</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8905,10 +8903,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.71942</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.71942</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8964,25 +8960,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L12-6</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.38795</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.38795</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router ko lagi   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -9083,10 +9075,8 @@
           <t>Ravi Bhagat</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9820991172</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9820991172</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9176,10 +9166,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
@@ -9190,7 +9178,7 @@
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : Replacement   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -9291,10 +9279,8 @@
           <t>Mandala International School</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9705404836</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9705404836</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9329,10 +9315,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.6982</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.6982</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -9388,25 +9372,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.27581</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.27581000000001</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9507,10 +9487,8 @@
           <t>Padam Roka</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9861027818</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9861027818</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9545,10 +9523,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.73035</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.73035</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9600,25 +9576,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.378552</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.378552</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>32</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>23</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.8%</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
@@ -832,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>9</v>
@@ -1057,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX45"/>
+  <dimension ref="A1:AX46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9624,6 +9624,214 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 3:10 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358878</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9741716174</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:10:39 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>CHB9741716174</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:51 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:10:39 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>New baneswor, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>9741716174@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -1051,13 +1051,13 @@
         <v>8</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX46"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9691,10 +9691,8 @@
           <t>Tanisha giri</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9741716174</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9741716174</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9766,10 +9764,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH46" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH46" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI46" s="3" t="inlineStr"/>
       <c r="AJ46" s="3" t="inlineStr"/>
@@ -9784,10 +9780,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
@@ -9798,35 +9792,351 @@
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS46" s="3" t="inlineStr">
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 3:24 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358900</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Smrity Bajracharya</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Smrity Bajracharya</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9842448307</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:24:25 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9842448307</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:30:56 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:24:25 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Siddha Pokhari Details from Google Maps Siddha Pokhari, Bhaktapur , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>smritiybaz@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>05:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>L31-4</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW46" s="3" t="inlineStr">
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>6h 53m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX46" s="3" t="inlineStr">
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 3:18 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifii 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr"/>
+      <c r="AA48" s="3" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr"/>
+      <c r="AC48" s="3" t="inlineStr"/>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr"/>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr"/>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr"/>
+      <c r="AM48" s="3" t="inlineStr"/>
+      <c r="AN48" s="3" t="inlineStr"/>
+      <c r="AO48" s="3" t="inlineStr"/>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifii 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9893,10 +9893,8 @@
           <t>Smrity Bajracharya</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9842448307</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9842448307</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9986,10 +9984,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
@@ -10000,7 +9996,7 @@
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
@@ -832,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>9</v>
@@ -1057,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10138,6 +10138,222 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359400</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Kumar Khati</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Kumar Khati</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9851037880</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:58:16 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9851037880</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 01:43:44 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:58:16 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.69608</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Next Ratna Rajya Secondary School , Baneshor , Kathmandu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>khatisk@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>02:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Isu Adhikari</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L52-4</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.33725</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2h 14m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10205,10 +10205,8 @@
           <t>Santosh Kumar Khati</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9851037880</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9851037880</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10243,10 +10241,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.69608</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.69608</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -10302,25 +10298,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>L52-4</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.33725</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.33725</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -848,22 +848,22 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="G3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -873,13 +873,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>1</v>
@@ -1051,13 +1051,13 @@
         <v>8</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX49"/>
+  <dimension ref="A1:AX50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10346,6 +10346,222 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Issue in youtube tv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Issue in youtube tv</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358268</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Sumita khadka</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Sumita khadka</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9743255647</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:24:46 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9851194078</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:08:11 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:24:46 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.688482</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Bode rishi talim kendra	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>06:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>L28-7</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.399965</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Issue in youtube tv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Issue in youtube tv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10413,10 +10413,8 @@
           <t>Sumita khadka</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9743255647</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9743255647</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10451,10 +10449,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.688482</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.688482</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10488,10 +10484,8 @@
           <t>General Query &amp; Feedback</t>
         </is>
       </c>
-      <c r="AH50" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH50" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI50" s="3" t="inlineStr">
         <is>
@@ -10510,25 +10504,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>L28-7</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.399965</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.39996499999999</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : Issue in youtube tv  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.0%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
@@ -832,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>9</v>
@@ -1057,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX50"/>
+  <dimension ref="A1:AX51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10552,6 +10552,222 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 5:15 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357811</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Bhim  Bahadur Bista</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Bhim  Bahadur Bista</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9847885658</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 05:15:56 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9841307132</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:19:20 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 05:15:56 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.66536</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>United School  F072, Lalitpur 44700 , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>agamanpista07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>07:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.33884</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 56m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_05_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>36</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX51"/>
+  <dimension ref="A1:AX52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10619,10 +10619,8 @@
           <t>Bhim  Bahadur Bista</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9847885658</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9847885658</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10657,10 +10655,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.66536</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.66536</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10716,53 +10712,157 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.33884</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.33884</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 56m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 56m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW51" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 5:22 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr"/>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr"/>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr"/>
+      <c r="V52" s="3" t="inlineStr"/>
+      <c r="W52" s="3" t="inlineStr"/>
+      <c r="X52" s="3" t="inlineStr"/>
+      <c r="Y52" s="3" t="inlineStr"/>
+      <c r="Z52" s="3" t="inlineStr"/>
+      <c r="AA52" s="3" t="inlineStr"/>
+      <c r="AB52" s="3" t="inlineStr"/>
+      <c r="AC52" s="3" t="inlineStr"/>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr"/>
+      <c r="AF52" s="3" t="inlineStr"/>
+      <c r="AG52" s="3" t="inlineStr"/>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr"/>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr"/>
+      <c r="AM52" s="3" t="inlineStr"/>
+      <c r="AN52" s="3" t="inlineStr"/>
+      <c r="AO52" s="3" t="inlineStr"/>
+      <c r="AP52" s="3" t="inlineStr"/>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
         </is>
